--- a/static/example_excel/import_subjects.xlsx
+++ b/static/example_excel/import_subjects.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -467,6 +467,21 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Видимість</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Кредити (скорочена)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Тип (скорочена)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -699,6 +714,85 @@
           <t>Залік</t>
         </is>
       </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>КР.01</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Курсова робота з фаху</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>20</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Залік</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>10</v>
+      </c>
+      <c r="G14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ОП.12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Практика в галузі (лише скорочена)</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Залік</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>скорочена</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ОП.13</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Військова підготовка (лише повна)</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Залік</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>повна</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
